--- a/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
@@ -87,12 +87,12 @@
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
+    <t xml:space="preserve">Coihueco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ranquil</t>
   </si>
   <si>
-    <t xml:space="preserve">Coihueco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:44</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>194.76</v>
+        <v>210.71</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>177.95</v>
+        <v>194.79</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>171.68</v>
+        <v>187.08</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>146.99</v>
+        <v>157.73</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>145.86</v>
+        <v>156.84</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +626,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>142.86</v>
+        <v>153.59</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>141.54</v>
+        <v>152.74</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>140.35</v>
+        <v>150.61</v>
       </c>
     </row>
     <row r="10">
@@ -677,7 +677,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>136.85</v>
+        <v>148.13</v>
       </c>
     </row>
     <row r="11">
@@ -694,7 +694,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>130.25</v>
+        <v>139.84</v>
       </c>
     </row>
     <row r="12">
@@ -711,7 +711,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>129.19</v>
+        <v>139.75</v>
       </c>
     </row>
     <row r="13">
@@ -728,7 +728,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>127.97</v>
+        <v>138.08</v>
       </c>
     </row>
     <row r="14">
@@ -745,7 +745,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>124.57</v>
+        <v>135.36</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>122.08</v>
+        <v>131.88</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>121.16</v>
+        <v>131.03</v>
       </c>
     </row>
     <row r="17">
@@ -796,7 +796,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>120.78</v>
+        <v>127.59</v>
       </c>
     </row>
     <row r="18">
@@ -813,7 +813,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>110.55</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19">
@@ -824,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>16206</v>
+        <v>16302</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>100.75</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="20">
@@ -841,13 +841,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16302</v>
+        <v>16206</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>100.19</v>
+        <v>106.71</v>
       </c>
     </row>
     <row r="21">
@@ -864,7 +864,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>86.78</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="22">
@@ -881,7 +881,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>73.13</v>
+        <v>76.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán Viejo</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:11</t>
+    <t xml:space="preserve">2026-10-04 10:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:44</t>
+    <t xml:space="preserve">2026-10-05 16:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
